--- a/converted/oylik/2026-02/Elektr Murojaatlar.xlsx
+++ b/converted/oylik/2026-02/Elektr Murojaatlar.xlsx
@@ -11,11 +11,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="148">
   <si>
     <t>Murojaatlar Fevral Holatiga Ko'ra</t>
   </si>
   <si>
+    <t>Podstansiya</t>
+  </si>
+  <si>
+    <t>Fider</t>
+  </si>
+  <si>
     <t>TP Nomi</t>
   </si>
   <si>
@@ -52,9 +58,18 @@
     <t>Ma'sul xodim (manba)</t>
   </si>
   <si>
+    <t>Eslatma</t>
+  </si>
+  <si>
     <t>Manba (fayl, qator)</t>
   </si>
   <si>
+    <t>Baliqchi</t>
+  </si>
+  <si>
+    <t>Sarkor</t>
+  </si>
+  <si>
     <t>415</t>
   </si>
   <si>
@@ -97,6 +112,9 @@
     <t>JASORAT MFY</t>
   </si>
   <si>
+    <t>TP 383 shu hududning Transformatorlar fayllarida ham, abonentlar reestrida ham yo'q - TP ga bog'lanmaydi</t>
+  </si>
+  <si>
     <t>baliqchi/7 oylik/Elektr Murojaatlar.xlsx, 24-qator</t>
   </si>
   <si>
@@ -112,6 +130,9 @@
     <t>268</t>
   </si>
   <si>
+    <t>TP 268 shu hududning Transformatorlar fayllarida yo'q - TP bo'sh qoldirildi</t>
+  </si>
+  <si>
     <t>baliqchi/7 oylik/Elektr Murojaatlar.xlsx, 25-qator</t>
   </si>
   <si>
@@ -130,9 +151,18 @@
     <t>OLIMBEK MFY</t>
   </si>
   <si>
+    <t>TP 91 shu hududning Transformatorlar fayllarida yo'q - TP bo'sh qoldirildi</t>
+  </si>
+  <si>
     <t>baliqchi/7 oylik/Elektr Murojaatlar.xlsx, 26-qator</t>
   </si>
   <si>
+    <t>O'rmonbek</t>
+  </si>
+  <si>
+    <t>G'alaba</t>
+  </si>
+  <si>
     <t>283</t>
   </si>
   <si>
@@ -163,6 +193,9 @@
     <t>baliqchi/7 oylik/Elektr Murojaatlar.xlsx, 28-qator</t>
   </si>
   <si>
+    <t>Oqqo'rg'on</t>
+  </si>
+  <si>
     <t>129</t>
   </si>
   <si>
@@ -190,6 +223,9 @@
     <t>290</t>
   </si>
   <si>
+    <t>TP 290 shu hududning Transformatorlar fayllarida yo'q - TP bo'sh qoldirildi</t>
+  </si>
+  <si>
     <t>baliqchi/7 oylik/Elektr Murojaatlar.xlsx, 30-qator</t>
   </si>
   <si>
@@ -223,6 +259,12 @@
     <t>baliqchi/7 oylik/Elektr Murojaatlar.xlsx, 32-qator</t>
   </si>
   <si>
+    <t>Chinobod</t>
+  </si>
+  <si>
+    <t>Tashlama</t>
+  </si>
+  <si>
     <t>293</t>
   </si>
   <si>
@@ -256,6 +298,12 @@
     <t>chinobod/Elektr Murojaatlar.xlsx [7 oy], 9-qator</t>
   </si>
   <si>
+    <t>Qo'shtepasaroy</t>
+  </si>
+  <si>
+    <t>Sirmoq</t>
+  </si>
+  <si>
     <t>160</t>
   </si>
   <si>
@@ -280,6 +328,9 @@
     <t>chinobod/Elektr Murojaatlar.xlsx [7 oy], 10-qator</t>
   </si>
   <si>
+    <t>Yangiqishloq</t>
+  </si>
+  <si>
     <t>197</t>
   </si>
   <si>
@@ -304,7 +355,10 @@
     <t>chinobod/Elektr Murojaatlar.xlsx [7 oy], 11-qator</t>
   </si>
   <si>
-    <t>166</t>
+    <t>Xaqulobod</t>
+  </si>
+  <si>
+    <t>44</t>
   </si>
   <si>
     <t>180700</t>
@@ -326,6 +380,9 @@
   </si>
   <si>
     <t>chinobod/Elektr Murojaatlar.xlsx [7 oy], 12-qator</t>
+  </si>
+  <si>
+    <t>Kamoliy</t>
   </si>
   <si>
     <t>113</t>
@@ -815,17 +872,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="14" style="1" customWidth="1"/>
-    <col min="5" max="5" width="34" customWidth="1"/>
-    <col min="6" max="7" width="22" customWidth="1"/>
-    <col min="8" max="13" width="26" customWidth="1"/>
+    <col min="1" max="5" width="22" customWidth="1"/>
+    <col min="6" max="6" width="14" style="1" customWidth="1"/>
+    <col min="7" max="7" width="34" customWidth="1"/>
+    <col min="8" max="9" width="22" customWidth="1"/>
+    <col min="10" max="16" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -841,8 +898,11 @@
       <c r="K1"/>
       <c r="L1"/>
       <c r="M1"/>
-    </row>
-    <row r="2" ht="45" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N1"/>
+      <c r="O1"/>
+      <c r="P1"/>
+    </row>
+    <row r="2" ht="45" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -864,10 +924,10 @@
       <c r="G2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="3" t="s">
         <v>9</v>
       </c>
       <c r="J2" s="4" t="s">
@@ -882,602 +942,689 @@
       <c r="M2" s="4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="1">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="1">
         <v>46058</v>
       </c>
-      <c r="E3" t="s">
+      <c r="G3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M3" t="s">
+        <v>26</v>
+      </c>
+      <c r="P3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="1">
+        <v>46069</v>
+      </c>
+      <c r="G4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M4" t="s">
+        <v>26</v>
+      </c>
+      <c r="O4" t="s">
+        <v>33</v>
+      </c>
+      <c r="P4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="4:16" x14ac:dyDescent="0.25">
+      <c r="D5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" s="1">
+        <v>46071</v>
+      </c>
+      <c r="G5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" t="s">
+        <v>38</v>
+      </c>
+      <c r="M5" t="s">
+        <v>26</v>
+      </c>
+      <c r="O5" t="s">
+        <v>39</v>
+      </c>
+      <c r="P5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="4:16" x14ac:dyDescent="0.25">
+      <c r="D6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" s="1">
+        <v>46073</v>
+      </c>
+      <c r="G6" t="s">
+        <v>43</v>
+      </c>
+      <c r="H6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6" t="s">
+        <v>44</v>
+      </c>
+      <c r="L6" t="s">
+        <v>45</v>
+      </c>
+      <c r="M6" t="s">
+        <v>26</v>
+      </c>
+      <c r="O6" t="s">
+        <v>46</v>
+      </c>
+      <c r="P6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" s="1">
+        <v>46076</v>
+      </c>
+      <c r="G7" t="s">
+        <v>53</v>
+      </c>
+      <c r="H7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M7" t="s">
+        <v>26</v>
+      </c>
+      <c r="P7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="4:16" x14ac:dyDescent="0.25">
+      <c r="D8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F8" s="1">
+        <v>46076</v>
+      </c>
+      <c r="G8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" t="s">
+        <v>58</v>
+      </c>
+      <c r="M8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>17</v>
       </c>
-      <c r="F3" t="s">
+      <c r="B9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E9" t="s">
+        <v>63</v>
+      </c>
+      <c r="F9" s="1">
+        <v>46077</v>
+      </c>
+      <c r="G9" t="s">
+        <v>64</v>
+      </c>
+      <c r="H9" t="s">
+        <v>23</v>
+      </c>
+      <c r="I9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" t="s">
+        <v>65</v>
+      </c>
+      <c r="M9" t="s">
+        <v>26</v>
+      </c>
+      <c r="P9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="4:16" x14ac:dyDescent="0.25">
+      <c r="D10" t="s">
+        <v>67</v>
+      </c>
+      <c r="E10" t="s">
+        <v>68</v>
+      </c>
+      <c r="F10" s="1">
+        <v>46078</v>
+      </c>
+      <c r="G10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I10" t="s">
+        <v>24</v>
+      </c>
+      <c r="J10" t="s">
+        <v>69</v>
+      </c>
+      <c r="L10" t="s">
+        <v>58</v>
+      </c>
+      <c r="M10" t="s">
+        <v>26</v>
+      </c>
+      <c r="O10" t="s">
+        <v>70</v>
+      </c>
+      <c r="P10" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="4:16" x14ac:dyDescent="0.25">
+      <c r="D11" t="s">
+        <v>72</v>
+      </c>
+      <c r="E11" t="s">
+        <v>73</v>
+      </c>
+      <c r="F11" s="1">
+        <v>46079</v>
+      </c>
+      <c r="G11" t="s">
+        <v>74</v>
+      </c>
+      <c r="H11" t="s">
+        <v>23</v>
+      </c>
+      <c r="I11" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11" t="s">
+        <v>75</v>
+      </c>
+      <c r="M11" t="s">
+        <v>26</v>
+      </c>
+      <c r="P11" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" t="s">
         <v>18</v>
       </c>
-      <c r="G3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="C12" t="s">
+        <v>77</v>
+      </c>
+      <c r="D12" t="s">
+        <v>78</v>
+      </c>
+      <c r="E12" t="s">
+        <v>79</v>
+      </c>
+      <c r="F12" s="1">
+        <v>46079</v>
+      </c>
+      <c r="G12" t="s">
+        <v>80</v>
+      </c>
+      <c r="H12" t="s">
         <v>23</v>
       </c>
-      <c r="B4" t="s">
+      <c r="I12" t="s">
         <v>24</v>
       </c>
-      <c r="C4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="1">
-        <v>46069</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="M12" t="s">
         <v>26</v>
       </c>
-      <c r="F4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" t="s">
-        <v>19</v>
-      </c>
-      <c r="J4" t="s">
-        <v>27</v>
-      </c>
-      <c r="K4" t="s">
-        <v>21</v>
-      </c>
-      <c r="M4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" s="1">
-        <v>46071</v>
-      </c>
-      <c r="E5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K5" t="s">
-        <v>21</v>
-      </c>
-      <c r="M5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" s="1">
-        <v>46073</v>
-      </c>
-      <c r="E6" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6" t="s">
-        <v>37</v>
-      </c>
-      <c r="J6" t="s">
-        <v>38</v>
-      </c>
-      <c r="K6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" s="1">
-        <v>46076</v>
-      </c>
-      <c r="E7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G7" t="s">
-        <v>19</v>
-      </c>
-      <c r="K7" t="s">
-        <v>21</v>
-      </c>
-      <c r="M7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C8" t="s">
-        <v>46</v>
-      </c>
-      <c r="D8" s="1">
-        <v>46076</v>
-      </c>
-      <c r="E8" t="s">
-        <v>47</v>
-      </c>
-      <c r="F8" t="s">
-        <v>18</v>
-      </c>
-      <c r="G8" t="s">
-        <v>19</v>
-      </c>
-      <c r="J8" t="s">
-        <v>48</v>
-      </c>
-      <c r="K8" t="s">
-        <v>21</v>
-      </c>
-      <c r="M8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>50</v>
-      </c>
-      <c r="B9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D9" s="1">
+      <c r="P12" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>82</v>
+      </c>
+      <c r="B13" t="s">
+        <v>83</v>
+      </c>
+      <c r="C13" t="s">
+        <v>84</v>
+      </c>
+      <c r="D13" t="s">
+        <v>85</v>
+      </c>
+      <c r="E13" t="s">
+        <v>86</v>
+      </c>
+      <c r="F13" s="1">
+        <v>46062</v>
+      </c>
+      <c r="G13" t="s">
+        <v>87</v>
+      </c>
+      <c r="H13" t="s">
+        <v>23</v>
+      </c>
+      <c r="I13" t="s">
+        <v>88</v>
+      </c>
+      <c r="J13" t="s">
+        <v>89</v>
+      </c>
+      <c r="K13" t="s">
+        <v>90</v>
+      </c>
+      <c r="L13" t="s">
+        <v>91</v>
+      </c>
+      <c r="M13" t="s">
+        <v>92</v>
+      </c>
+      <c r="N13" t="s">
+        <v>93</v>
+      </c>
+      <c r="P13" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>95</v>
+      </c>
+      <c r="B14" t="s">
+        <v>96</v>
+      </c>
+      <c r="C14" t="s">
+        <v>97</v>
+      </c>
+      <c r="D14" t="s">
+        <v>98</v>
+      </c>
+      <c r="E14" t="s">
+        <v>99</v>
+      </c>
+      <c r="F14" s="1">
         <v>46077</v>
       </c>
-      <c r="E9" t="s">
-        <v>53</v>
-      </c>
-      <c r="F9" t="s">
-        <v>18</v>
-      </c>
-      <c r="G9" t="s">
-        <v>19</v>
-      </c>
-      <c r="J9" t="s">
-        <v>54</v>
-      </c>
-      <c r="K9" t="s">
-        <v>21</v>
-      </c>
-      <c r="M9" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>56</v>
-      </c>
-      <c r="C10" t="s">
-        <v>57</v>
-      </c>
-      <c r="D10" s="1">
+      <c r="G14" t="s">
+        <v>100</v>
+      </c>
+      <c r="H14" t="s">
+        <v>23</v>
+      </c>
+      <c r="I14" t="s">
+        <v>88</v>
+      </c>
+      <c r="J14" t="s">
+        <v>101</v>
+      </c>
+      <c r="K14" t="s">
+        <v>102</v>
+      </c>
+      <c r="L14" t="s">
+        <v>103</v>
+      </c>
+      <c r="M14" t="s">
+        <v>92</v>
+      </c>
+      <c r="N14" t="s">
+        <v>93</v>
+      </c>
+      <c r="P14" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>95</v>
+      </c>
+      <c r="B15" t="s">
+        <v>105</v>
+      </c>
+      <c r="C15" t="s">
+        <v>106</v>
+      </c>
+      <c r="D15" t="s">
+        <v>107</v>
+      </c>
+      <c r="E15" t="s">
+        <v>108</v>
+      </c>
+      <c r="F15" s="1">
         <v>46078</v>
       </c>
-      <c r="E10" t="s">
-        <v>47</v>
-      </c>
-      <c r="F10" t="s">
-        <v>18</v>
-      </c>
-      <c r="G10" t="s">
-        <v>19</v>
-      </c>
-      <c r="H10" t="s">
-        <v>58</v>
-      </c>
-      <c r="J10" t="s">
-        <v>48</v>
-      </c>
-      <c r="K10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
-        <v>60</v>
-      </c>
-      <c r="C11" t="s">
-        <v>61</v>
-      </c>
-      <c r="D11" s="1">
+      <c r="G15" t="s">
+        <v>109</v>
+      </c>
+      <c r="H15" t="s">
+        <v>23</v>
+      </c>
+      <c r="I15" t="s">
+        <v>88</v>
+      </c>
+      <c r="J15" t="s">
+        <v>110</v>
+      </c>
+      <c r="K15" t="s">
+        <v>111</v>
+      </c>
+      <c r="L15" t="s">
+        <v>112</v>
+      </c>
+      <c r="M15" t="s">
+        <v>92</v>
+      </c>
+      <c r="N15" t="s">
+        <v>93</v>
+      </c>
+      <c r="P15" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>82</v>
+      </c>
+      <c r="B16" t="s">
+        <v>114</v>
+      </c>
+      <c r="C16" t="s">
+        <v>115</v>
+      </c>
+      <c r="D16" t="s">
+        <v>116</v>
+      </c>
+      <c r="E16" t="s">
+        <v>117</v>
+      </c>
+      <c r="F16" s="1">
         <v>46079</v>
       </c>
-      <c r="E11" t="s">
-        <v>62</v>
-      </c>
-      <c r="F11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G11" t="s">
-        <v>19</v>
-      </c>
-      <c r="J11" t="s">
-        <v>63</v>
-      </c>
-      <c r="K11" t="s">
-        <v>21</v>
-      </c>
-      <c r="M11" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>65</v>
-      </c>
-      <c r="B12" t="s">
-        <v>66</v>
-      </c>
-      <c r="C12" t="s">
-        <v>67</v>
-      </c>
-      <c r="D12" s="1">
+      <c r="G16" t="s">
+        <v>118</v>
+      </c>
+      <c r="H16" t="s">
+        <v>23</v>
+      </c>
+      <c r="I16" t="s">
+        <v>88</v>
+      </c>
+      <c r="J16" t="s">
+        <v>119</v>
+      </c>
+      <c r="K16" t="s">
+        <v>120</v>
+      </c>
+      <c r="L16" t="s">
+        <v>121</v>
+      </c>
+      <c r="M16" t="s">
+        <v>92</v>
+      </c>
+      <c r="N16" t="s">
+        <v>93</v>
+      </c>
+      <c r="P16" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>82</v>
+      </c>
+      <c r="B17" t="s">
+        <v>123</v>
+      </c>
+      <c r="C17" t="s">
+        <v>124</v>
+      </c>
+      <c r="D17" t="s">
+        <v>125</v>
+      </c>
+      <c r="E17" t="s">
+        <v>126</v>
+      </c>
+      <c r="F17" s="1">
         <v>46079</v>
       </c>
-      <c r="E12" t="s">
-        <v>68</v>
-      </c>
-      <c r="F12" t="s">
-        <v>18</v>
-      </c>
-      <c r="G12" t="s">
-        <v>19</v>
-      </c>
-      <c r="K12" t="s">
-        <v>21</v>
-      </c>
-      <c r="M12" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>70</v>
-      </c>
-      <c r="B13" t="s">
-        <v>71</v>
-      </c>
-      <c r="C13" t="s">
-        <v>72</v>
-      </c>
-      <c r="D13" s="1">
-        <v>46062</v>
-      </c>
-      <c r="E13" t="s">
-        <v>73</v>
-      </c>
-      <c r="F13" t="s">
-        <v>18</v>
-      </c>
-      <c r="G13" t="s">
-        <v>74</v>
-      </c>
-      <c r="H13" t="s">
-        <v>75</v>
-      </c>
-      <c r="I13" t="s">
-        <v>76</v>
-      </c>
-      <c r="J13" t="s">
-        <v>77</v>
-      </c>
-      <c r="K13" t="s">
-        <v>78</v>
-      </c>
-      <c r="L13" t="s">
-        <v>79</v>
-      </c>
-      <c r="M13" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>81</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="G17" t="s">
+        <v>127</v>
+      </c>
+      <c r="H17" t="s">
+        <v>23</v>
+      </c>
+      <c r="I17" t="s">
+        <v>88</v>
+      </c>
+      <c r="J17" t="s">
+        <v>128</v>
+      </c>
+      <c r="K17" t="s">
+        <v>129</v>
+      </c>
+      <c r="L17" t="s">
+        <v>130</v>
+      </c>
+      <c r="M17" t="s">
+        <v>92</v>
+      </c>
+      <c r="N17" t="s">
+        <v>93</v>
+      </c>
+      <c r="P17" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>82</v>
-      </c>
-      <c r="C14" t="s">
-        <v>83</v>
-      </c>
-      <c r="D14" s="1">
-        <v>46077</v>
-      </c>
-      <c r="E14" t="s">
-        <v>84</v>
-      </c>
-      <c r="F14" t="s">
-        <v>18</v>
-      </c>
-      <c r="G14" t="s">
-        <v>74</v>
-      </c>
-      <c r="H14" t="s">
-        <v>85</v>
-      </c>
-      <c r="I14" t="s">
-        <v>86</v>
-      </c>
-      <c r="J14" t="s">
-        <v>87</v>
-      </c>
-      <c r="K14" t="s">
-        <v>78</v>
-      </c>
-      <c r="L14" t="s">
-        <v>79</v>
-      </c>
-      <c r="M14" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>89</v>
-      </c>
-      <c r="B15" t="s">
-        <v>90</v>
-      </c>
-      <c r="C15" t="s">
-        <v>91</v>
-      </c>
-      <c r="D15" s="1">
-        <v>46078</v>
-      </c>
-      <c r="E15" t="s">
-        <v>92</v>
-      </c>
-      <c r="F15" t="s">
-        <v>18</v>
-      </c>
-      <c r="G15" t="s">
-        <v>74</v>
-      </c>
-      <c r="H15" t="s">
-        <v>93</v>
-      </c>
-      <c r="I15" t="s">
-        <v>94</v>
-      </c>
-      <c r="J15" t="s">
-        <v>95</v>
-      </c>
-      <c r="K15" t="s">
-        <v>78</v>
-      </c>
-      <c r="L15" t="s">
-        <v>79</v>
-      </c>
-      <c r="M15" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>97</v>
-      </c>
-      <c r="B16" t="s">
-        <v>98</v>
-      </c>
-      <c r="C16" t="s">
-        <v>99</v>
-      </c>
-      <c r="D16" s="1">
-        <v>46079</v>
-      </c>
-      <c r="E16" t="s">
-        <v>100</v>
-      </c>
-      <c r="F16" t="s">
-        <v>18</v>
-      </c>
-      <c r="G16" t="s">
-        <v>74</v>
-      </c>
-      <c r="H16" t="s">
-        <v>101</v>
-      </c>
-      <c r="I16" t="s">
-        <v>102</v>
-      </c>
-      <c r="J16" t="s">
-        <v>103</v>
-      </c>
-      <c r="K16" t="s">
-        <v>78</v>
-      </c>
-      <c r="L16" t="s">
-        <v>79</v>
-      </c>
-      <c r="M16" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>105</v>
-      </c>
-      <c r="B17" t="s">
-        <v>106</v>
-      </c>
-      <c r="C17" t="s">
-        <v>107</v>
-      </c>
-      <c r="D17" s="1">
-        <v>46079</v>
-      </c>
-      <c r="E17" t="s">
-        <v>108</v>
-      </c>
-      <c r="F17" t="s">
-        <v>18</v>
-      </c>
-      <c r="G17" t="s">
-        <v>74</v>
-      </c>
-      <c r="H17" t="s">
-        <v>109</v>
-      </c>
-      <c r="I17" t="s">
-        <v>110</v>
-      </c>
-      <c r="J17" t="s">
-        <v>111</v>
-      </c>
-      <c r="K17" t="s">
-        <v>78</v>
-      </c>
-      <c r="L17" t="s">
-        <v>79</v>
-      </c>
-      <c r="M17" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>113</v>
       </c>
       <c r="B18" t="s">
         <v>114</v>
       </c>
       <c r="C18" t="s">
-        <v>115</v>
-      </c>
-      <c r="D18" s="1">
+        <v>132</v>
+      </c>
+      <c r="D18" t="s">
+        <v>133</v>
+      </c>
+      <c r="E18" t="s">
+        <v>134</v>
+      </c>
+      <c r="F18" s="1">
         <v>46080</v>
       </c>
-      <c r="E18" t="s">
-        <v>116</v>
-      </c>
-      <c r="F18" t="s">
-        <v>18</v>
-      </c>
       <c r="G18" t="s">
-        <v>74</v>
+        <v>135</v>
       </c>
       <c r="H18" t="s">
-        <v>117</v>
+        <v>23</v>
       </c>
       <c r="I18" t="s">
-        <v>118</v>
+        <v>88</v>
       </c>
       <c r="J18" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="K18" t="s">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="L18" t="s">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="M18" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+      <c r="N18" t="s">
+        <v>93</v>
+      </c>
+      <c r="P18" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>121</v>
+        <v>82</v>
       </c>
       <c r="B19" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="C19" t="s">
-        <v>123</v>
-      </c>
-      <c r="D19" s="1">
+        <v>140</v>
+      </c>
+      <c r="D19" t="s">
+        <v>141</v>
+      </c>
+      <c r="E19" t="s">
+        <v>142</v>
+      </c>
+      <c r="F19" s="1">
         <v>46080</v>
       </c>
-      <c r="E19" t="s">
-        <v>124</v>
-      </c>
-      <c r="F19" t="s">
-        <v>18</v>
-      </c>
       <c r="G19" t="s">
-        <v>74</v>
+        <v>143</v>
       </c>
       <c r="H19" t="s">
-        <v>125</v>
+        <v>23</v>
       </c>
       <c r="I19" t="s">
-        <v>126</v>
+        <v>88</v>
       </c>
       <c r="J19" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="K19" t="s">
-        <v>78</v>
+        <v>145</v>
       </c>
       <c r="L19" t="s">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="M19" t="s">
-        <v>128</v>
+        <v>92</v>
+      </c>
+      <c r="N19" t="s">
+        <v>93</v>
+      </c>
+      <c r="P19" t="s">
+        <v>147</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A1:P1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
